--- a/output/pdf_financials_xlsx/LAC.xlsx
+++ b/output/pdf_financials_xlsx/LAC.xlsx
@@ -5119,10 +5119,10 @@
         <v>-0.198</v>
       </c>
       <c r="C103" s="3" t="n">
-        <v>0.116</v>
+        <v>0.018</v>
       </c>
       <c r="D103" s="3" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="E103" s="3" t="n">
         <v>0</v>
@@ -5134,22 +5134,22 @@
         <v>0</v>
       </c>
       <c r="H103" s="3" t="n">
-        <v>0</v>
+        <v>0.134</v>
       </c>
       <c r="I103" s="3" t="n">
-        <v>0</v>
+        <v>-0.754</v>
       </c>
       <c r="J103" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K103" s="3" t="n">
-        <v>0</v>
+        <v>-0.643</v>
       </c>
       <c r="L103" s="3" t="n">
-        <v>0</v>
+        <v>0.301</v>
       </c>
       <c r="M103" s="3" t="n">
-        <v>0</v>
+        <v>0.127</v>
       </c>
     </row>
     <row r="104">
@@ -5248,10 +5248,10 @@
         <v>0.118</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>-0.759</v>
+        <v>-0.857</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>-0.552</v>
+        <v>-0.512</v>
       </c>
       <c r="E106" s="3" t="n">
         <v>0.845</v>
@@ -5263,22 +5263,22 @@
         <v>0.214</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>4</v>
+        <v>4.134</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>2.648</v>
+        <v>1.894</v>
       </c>
       <c r="J106" s="3" t="n">
         <v>11.187</v>
       </c>
       <c r="K106" s="3" t="n">
-        <v>-3.424</v>
+        <v>-4.067</v>
       </c>
       <c r="L106" s="3" t="n">
-        <v>13.61</v>
+        <v>13.911</v>
       </c>
       <c r="M106" s="3" t="n">
-        <v>7.018</v>
+        <v>7.145</v>
       </c>
     </row>
     <row r="107">
@@ -6906,7 +6906,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>-</t>
@@ -9096,7 +9100,11 @@
           <t>Prepaids and deposits (Note 7)</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>-</t>
@@ -10412,7 +10420,11 @@
           <t>Receivables, prepaids and deposits</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
           <t>-</t>
@@ -20020,7 +20032,11 @@
           <t>Decrease in prepaids and deposits</t>
         </is>
       </c>
-      <c r="D182" t="inlineStr"/>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E182" t="inlineStr">
         <is>
           <t>-</t>
@@ -21522,7 +21538,11 @@
           <t>(Increase)/decrease in prepaids and deposits</t>
         </is>
       </c>
-      <c r="D202" t="inlineStr"/>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E202" t="inlineStr">
         <is>
           <t>-</t>
@@ -24334,7 +24354,11 @@
           <t>(Increase)/decrease in receivables, prepaids and deposits</t>
         </is>
       </c>
-      <c r="D239" t="inlineStr"/>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E239" t="inlineStr">
         <is>
           <t>-</t>
@@ -29622,7 +29646,11 @@
           <t>Decrease in receivables, prepaids and deposits</t>
         </is>
       </c>
-      <c r="D309" t="inlineStr"/>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E309" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/LAC.xlsx
+++ b/output/pdf_financials_xlsx/LAC.xlsx
@@ -2158,7 +2158,7 @@
         <v>593.885</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>568.226</v>
       </c>
     </row>
     <row r="35">
@@ -2244,7 +2244,7 @@
         <v>593.885</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>568.226</v>
       </c>
     </row>
     <row r="37">
@@ -2760,7 +2760,7 @@
         <v>8.021000000000001</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>907.529</v>
+        <v>339.303</v>
       </c>
     </row>
     <row r="49">
@@ -6027,13 +6027,13 @@
         </is>
       </c>
       <c r="B124" s="3" t="n">
-        <v>0</v>
+        <v>-0.014</v>
       </c>
       <c r="C124" s="3" t="n">
-        <v>0</v>
+        <v>-0.036</v>
       </c>
       <c r="D124" s="3" t="n">
-        <v>0</v>
+        <v>-0.052</v>
       </c>
       <c r="E124" s="3" t="n">
         <v>0</v>
@@ -6070,13 +6070,13 @@
         </is>
       </c>
       <c r="B125" s="3" t="n">
-        <v>0</v>
+        <v>-0.014</v>
       </c>
       <c r="C125" s="3" t="n">
-        <v>0</v>
+        <v>-0.036</v>
       </c>
       <c r="D125" s="3" t="n">
-        <v>0</v>
+        <v>-0.052</v>
       </c>
       <c r="E125" s="3" t="n">
         <v>0</v>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -30490,7 +30490,11 @@
           <t>Finance lease repayments</t>
         </is>
       </c>
-      <c r="D320" t="inlineStr"/>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E320" s="5" t="n">
         <v>-0.014</v>
       </c>
@@ -34064,7 +34068,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">

--- a/output/pdf_financials_xlsx/LAC.xlsx
+++ b/output/pdf_financials_xlsx/LAC.xlsx
@@ -1440,11 +1440,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H20" s="3" t="n">
-        <v>-36.234</v>
-      </c>
-      <c r="I20" s="3" t="n">
-        <v>-38.488</v>
+      <c r="H20" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I20" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J20" s="1" t="inlineStr">
         <is>
@@ -1494,10 +1498,10 @@
         </is>
       </c>
       <c r="H21" s="3" t="n">
-        <v>0</v>
+        <v>-35.221</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>0</v>
+        <v>0.122</v>
       </c>
       <c r="J21" s="1" t="inlineStr">
         <is>
@@ -3165,13 +3169,13 @@
         <v>0</v>
       </c>
       <c r="K57" s="3" t="n">
-        <v>0</v>
+        <v>2.252</v>
       </c>
       <c r="L57" s="3" t="n">
-        <v>0</v>
+        <v>3.711</v>
       </c>
       <c r="M57" s="3" t="n">
-        <v>0</v>
+        <v>14.223</v>
       </c>
     </row>
     <row r="58">
@@ -35218,7 +35222,11 @@
           <t>INCOME FROM DISCONTINUED OPERATIONS</t>
         </is>
       </c>
-      <c r="D382" t="inlineStr"/>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E382" t="inlineStr">
         <is>
           <t>-</t>
@@ -36932,7 +36940,11 @@
           <t>NET LOSS BEFORE DISCONTINUED OPERATIONS</t>
         </is>
       </c>
-      <c r="D405" t="inlineStr"/>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E405" t="inlineStr">
         <is>
           <t>-</t>
